--- a/conformance/fixtures/088-date-comparison-equality/data.xlsx
+++ b/conformance/fixtures/088-date-comparison-equality/data.xlsx
@@ -419,7 +419,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>46149.625</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -427,7 +427,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>46150.625</v>
+        <v>46151</v>
       </c>
     </row>
   </sheetData>
